--- a/samples/Q_科目余额表.xlsx
+++ b/samples/Q_科目余额表.xlsx
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>无形资产原值</t>
+          <t>无形资产</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -511,13 +511,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>200000</v>
+        <v>800000</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3700000</v>
+        <v>4300000</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -526,31 +526,151 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>170101</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>无形资产-土地使用权</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>170102</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>无形资产-专利权</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>170103</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>无形资产-软件</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>累计摊销</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1600000</v>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>980000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1240000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>无形资产减值准备</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/samples/Q_科目余额表.xlsx
+++ b/samples/Q_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
